--- a/data-source/不可升级建筑数据.xlsx
+++ b/data-source/不可升级建筑数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6803E365-0887-4D1C-A005-D9FCA7BE9AE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2056DC9-666D-4F33-8FCE-20643FA7CA19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{345D919C-BD97-4FB0-A520-39D64B4D9066}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="203">
   <si>
     <t>建筑名称</t>
   </si>
@@ -645,6 +645,9 @@
   </si>
   <si>
     <t>商店购买；黑色星期五；箱子</t>
+  </si>
+  <si>
+    <t>炉架*4；原松木*4；碎铜片*4；铜矿石*4</t>
   </si>
 </sst>
 </file>
@@ -1284,13 +1287,13 @@
         <v>9</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>22</v>
+        <v>202</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>

--- a/data-source/不可升级建筑数据.xlsx
+++ b/data-source/不可升级建筑数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2056DC9-666D-4F33-8FCE-20643FA7CA19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A2C1316-548E-4BB3-BCFA-0E4172DFDF7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{345D919C-BD97-4FB0-A520-39D64B4D9066}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="204">
   <si>
     <t>建筑名称</t>
   </si>
@@ -413,9 +413,6 @@
     <t>棺材宝箱（蓝）</t>
   </si>
   <si>
-    <t>庆祝游戏1周年的纪念宝箱</t>
-  </si>
-  <si>
     <t>庆祝游戏2周年的纪念宝箱</t>
   </si>
   <si>
@@ -590,9 +587,6 @@
     <t>瘟疫之神的忠实追随者拥有的战利品存储室</t>
   </si>
   <si>
-    <t>一周年纪念宝箱</t>
-  </si>
-  <si>
     <t>二周年纪念宝箱</t>
   </si>
   <si>
@@ -648,6 +642,15 @@
   </si>
   <si>
     <t>炉架*4；原松木*4；碎铜片*4；铜矿石*4</t>
+  </si>
+  <si>
+    <t>红宝箱</t>
+  </si>
+  <si>
+    <t>商店购买；红猎；箱子</t>
+  </si>
+  <si>
+    <t>宝箱的价格无法与内容物的价值相提并论，仅第一二季红猎出现过</t>
   </si>
 </sst>
 </file>
@@ -1201,7 +1204,7 @@
         <v>17</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>12</v>
@@ -1245,7 +1248,7 @@
         <v>20</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>5</v>
@@ -1287,7 +1290,7 @@
         <v>9</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>6</v>
@@ -1463,7 +1466,7 @@
         <v>100</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>28</v>
@@ -1835,7 +1838,7 @@
         <v>100</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>57</v>
@@ -2022,7 +2025,7 @@
         <v>100</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>22</v>
@@ -2061,7 +2064,7 @@
         <v>3</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>80</v>
@@ -2100,7 +2103,7 @@
         <v>999</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>22</v>
@@ -2411,7 +2414,7 @@
         <v>999</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>22</v>
@@ -2423,7 +2426,7 @@
         <v>22</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="J35" s="1"/>
     </row>
@@ -2441,7 +2444,7 @@
         <v>999</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>22</v>
@@ -2453,7 +2456,7 @@
         <v>22</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="J36" s="1"/>
     </row>
@@ -2471,7 +2474,7 @@
         <v>999</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>22</v>
@@ -2483,7 +2486,7 @@
         <v>22</v>
       </c>
       <c r="I37" s="10" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="J37" s="1"/>
     </row>
@@ -2501,7 +2504,7 @@
         <v>999</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>22</v>
@@ -2513,7 +2516,7 @@
         <v>22</v>
       </c>
       <c r="I38" s="10" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="J38" s="1"/>
     </row>
@@ -2531,7 +2534,7 @@
         <v>999</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>22</v>
@@ -2543,13 +2546,13 @@
         <v>22</v>
       </c>
       <c r="I39" s="10" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="J39" s="1"/>
     </row>
     <row r="40" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A40" s="8" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="B40" s="1">
         <v>200</v>
@@ -2560,8 +2563,8 @@
       <c r="D40" s="1">
         <v>999</v>
       </c>
-      <c r="E40" s="1" t="s">
-        <v>124</v>
+      <c r="E40" s="7" t="s">
+        <v>203</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>22</v>
@@ -2573,13 +2576,13 @@
         <v>22</v>
       </c>
       <c r="I40" s="10" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="J40" s="1"/>
     </row>
-    <row r="41" spans="1:10" ht="27" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B41" s="1">
         <v>200</v>
@@ -2591,7 +2594,7 @@
         <v>999</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>22</v>
@@ -2603,13 +2606,13 @@
         <v>22</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="J41" s="1"/>
     </row>
     <row r="42" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B42" s="1">
         <v>200</v>
@@ -2621,7 +2624,7 @@
         <v>999</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>22</v>
@@ -2633,13 +2636,13 @@
         <v>22</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="J42" s="1"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B43" s="1">
         <v>200</v>
@@ -2651,7 +2654,7 @@
         <v>999</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>22</v>
@@ -2663,13 +2666,13 @@
         <v>22</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="J43" s="1"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B44" s="1">
         <v>200</v>
@@ -2681,7 +2684,7 @@
         <v>999</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>22</v>
@@ -2693,13 +2696,13 @@
         <v>22</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="J44" s="1"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B45" s="1">
         <v>200</v>
@@ -2711,7 +2714,7 @@
         <v>999</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>22</v>
@@ -2723,13 +2726,13 @@
         <v>22</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="J45" s="1"/>
     </row>
     <row r="46" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B46" s="1">
         <v>300</v>
@@ -2741,7 +2744,7 @@
         <v>999</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>22</v>
@@ -2753,13 +2756,13 @@
         <v>22</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="J46" s="1"/>
     </row>
     <row r="47" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A47" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B47" s="1">
         <v>200</v>
@@ -2771,7 +2774,7 @@
         <v>999</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>22</v>
@@ -2783,13 +2786,13 @@
         <v>22</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="J47" s="1"/>
     </row>
     <row r="48" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B48" s="1">
         <v>200</v>
@@ -2801,7 +2804,7 @@
         <v>999</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>22</v>
@@ -2813,13 +2816,13 @@
         <v>22</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="J48" s="1"/>
     </row>
     <row r="49" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A49" s="8" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B49" s="1">
         <v>200</v>
@@ -2831,7 +2834,7 @@
         <v>999</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>22</v>
@@ -2843,13 +2846,13 @@
         <v>22</v>
       </c>
       <c r="I49" s="10" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="J49" s="1"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B50" s="1">
         <v>200</v>
@@ -2861,7 +2864,7 @@
         <v>999</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>22</v>
@@ -2873,13 +2876,13 @@
         <v>22</v>
       </c>
       <c r="I50" s="10" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="J50" s="1"/>
     </row>
     <row r="51" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A51" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B51" s="1">
         <v>200</v>
@@ -2891,7 +2894,7 @@
         <v>999</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>22</v>
@@ -2903,13 +2906,13 @@
         <v>22</v>
       </c>
       <c r="I51" s="10" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="J51" s="1"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B52" s="1">
         <v>200</v>
@@ -2921,7 +2924,7 @@
         <v>999</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>22</v>
@@ -2933,13 +2936,13 @@
         <v>22</v>
       </c>
       <c r="I52" s="10" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="J52" s="1"/>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B53" s="1">
         <v>200</v>
@@ -2951,7 +2954,7 @@
         <v>999</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>22</v>
@@ -2963,13 +2966,13 @@
         <v>22</v>
       </c>
       <c r="I53" s="10" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="J53" s="1"/>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B54" s="1">
         <v>200</v>
@@ -2981,7 +2984,7 @@
         <v>999</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>22</v>
@@ -2993,13 +2996,13 @@
         <v>22</v>
       </c>
       <c r="I54" s="10" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="J54" s="1"/>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B55" s="1">
         <v>200</v>
@@ -3011,7 +3014,7 @@
         <v>999</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>22</v>
@@ -3023,13 +3026,13 @@
         <v>22</v>
       </c>
       <c r="I55" s="10" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="J55" s="1"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B56" s="1">
         <v>200</v>
@@ -3041,7 +3044,7 @@
         <v>999</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>22</v>
@@ -3053,13 +3056,13 @@
         <v>22</v>
       </c>
       <c r="I56" s="10" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="J56" s="1"/>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B57" s="1">
         <v>200</v>
@@ -3071,7 +3074,7 @@
         <v>999</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>22</v>
@@ -3083,13 +3086,13 @@
         <v>22</v>
       </c>
       <c r="I57" s="10" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="J57" s="1"/>
     </row>
     <row r="58" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A58" s="11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B58" s="1">
         <v>200</v>
@@ -3101,7 +3104,7 @@
         <v>999</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F58" s="1"/>
       <c r="G58" s="1" t="s">
@@ -3111,13 +3114,13 @@
         <v>22</v>
       </c>
       <c r="I58" s="10" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="J58" s="1"/>
     </row>
     <row r="59" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A59" s="11" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B59" s="1">
         <v>200</v>
@@ -3129,7 +3132,7 @@
         <v>999</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>22</v>
@@ -3141,13 +3144,13 @@
         <v>22</v>
       </c>
       <c r="I59" s="10" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="J59" s="1"/>
     </row>
     <row r="60" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A60" s="11" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B60" s="1">
         <v>200</v>
@@ -3159,7 +3162,7 @@
         <v>999</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>22</v>
@@ -3171,13 +3174,13 @@
         <v>22</v>
       </c>
       <c r="I60" s="10" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="J60" s="1"/>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B61" s="1">
         <v>200</v>
@@ -3189,7 +3192,7 @@
         <v>999</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>22</v>
@@ -3201,13 +3204,13 @@
         <v>22</v>
       </c>
       <c r="I61" s="10" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="J61" s="1"/>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B62" s="1">
         <v>200</v>
@@ -3219,7 +3222,7 @@
         <v>999</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>22</v>
@@ -3231,13 +3234,13 @@
         <v>22</v>
       </c>
       <c r="I62" s="10" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="J62" s="1"/>
     </row>
     <row r="63" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A63" s="11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B63" s="1">
         <v>200</v>
@@ -3249,7 +3252,7 @@
         <v>999</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>22</v>
@@ -3261,13 +3264,13 @@
         <v>22</v>
       </c>
       <c r="I63" s="10" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J63" s="1"/>
     </row>
     <row r="64" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A64" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B64" s="1">
         <v>200</v>
@@ -3279,7 +3282,7 @@
         <v>999</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>22</v>
@@ -3291,13 +3294,13 @@
         <v>22</v>
       </c>
       <c r="I64" s="10" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="J64" s="1"/>
     </row>
     <row r="65" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A65" s="11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B65" s="1">
         <v>200</v>
@@ -3309,7 +3312,7 @@
         <v>999</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>22</v>
@@ -3321,13 +3324,13 @@
         <v>22</v>
       </c>
       <c r="I65" s="10" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="J65" s="1"/>
     </row>
     <row r="66" spans="1:10" ht="27" x14ac:dyDescent="0.3">
       <c r="A66" s="11" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B66" s="1">
         <v>200</v>
@@ -3339,7 +3342,7 @@
         <v>999</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>22</v>
@@ -3351,13 +3354,13 @@
         <v>22</v>
       </c>
       <c r="I66" s="10" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="J66" s="1"/>
     </row>
     <row r="67" spans="1:10" ht="27.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A67" s="12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B67" s="13">
         <v>200</v>
@@ -3369,7 +3372,7 @@
         <v>999</v>
       </c>
       <c r="E67" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F67" s="13" t="s">
         <v>22</v>
@@ -3381,7 +3384,7 @@
         <v>22</v>
       </c>
       <c r="I67" s="14" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="J67" s="1"/>
     </row>

--- a/data-source/不可升级建筑数据.xlsx
+++ b/data-source/不可升级建筑数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A2C1316-548E-4BB3-BCFA-0E4172DFDF7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0808E49-525D-4DB0-84BE-2D3F30D6E5DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{345D919C-BD97-4FB0-A520-39D64B4D9066}"/>
   </bookViews>
@@ -3336,7 +3336,7 @@
         <v>200</v>
       </c>
       <c r="C66" s="1">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D66" s="1">
         <v>999</v>
